--- a/Code/Inventor( ) Object Class Map.xlsx
+++ b/Code/Inventor( ) Object Class Map.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b0778c8abf470420/_Hobby/MicroPython/Github/Inventor 2040 W/Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{AB2F4A40-CEDE-4481-A7CA-81FB681293B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49A5AF99-6893-4297-BB87-D74F5C65E812}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{AB2F4A40-CEDE-4481-A7CA-81FB681293B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{554A750B-BFFF-4194-AFDA-346DB84EF057}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{8EFCF243-6549-4933-AAE3-AD4016C4DA94}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t xml:space="preserve">  &lt;function switch_pressed at 0x20010380&gt;</t>
   </si>
   <si>
-    <t>(6, 7)</t>
-  </si>
-  <si>
     <t xml:space="preserve">  &lt;function play_tone at 0x20010410&gt;</t>
   </si>
   <si>
@@ -225,6 +222,9 @@
   </si>
   <si>
     <t>Returns:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (6, 7)</t>
   </si>
 </sst>
 </file>
@@ -675,7 +675,7 @@
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
@@ -683,22 +683,22 @@
         <v>1</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
       <c r="D5" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>59</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>2</v>
@@ -706,15 +706,15 @@
     </row>
     <row r="7" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>4</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="9" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" s="2">
         <v>4</v>
@@ -730,7 +730,7 @@
     </row>
     <row r="10" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2">
         <v>3</v>
@@ -738,7 +738,7 @@
     </row>
     <row r="11" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2">
         <v>0.2</v>
@@ -746,7 +746,7 @@
     </row>
     <row r="12" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -754,15 +754,15 @@
     </row>
     <row r="13" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -770,15 +770,15 @@
     </row>
     <row r="15" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B16" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C16" s="2">
         <v>5</v>
@@ -786,7 +786,7 @@
     </row>
     <row r="17" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B17" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="2">
         <v>4</v>
@@ -794,7 +794,7 @@
     </row>
     <row r="18" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2">
         <v>20</v>
@@ -802,7 +802,7 @@
     </row>
     <row r="19" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B19" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -810,15 +810,15 @@
     </row>
     <row r="20" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B20" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>6</v>
+        <v>60</v>
       </c>
     </row>
     <row r="21" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B21" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -826,39 +826,39 @@
     </row>
     <row r="22" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="2">
         <v>21</v>
@@ -866,7 +866,7 @@
     </row>
     <row r="27" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B27" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27" s="2">
         <v>10</v>
@@ -874,7 +874,7 @@
     </row>
     <row r="28" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B28" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28" s="2">
         <v>11</v>
@@ -882,7 +882,7 @@
     </row>
     <row r="29" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B29" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="2">
         <v>12</v>
@@ -890,7 +890,7 @@
     </row>
     <row r="30" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C30" s="2">
         <v>13</v>
@@ -898,7 +898,7 @@
     </row>
     <row r="31" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="2">
         <v>14</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="32" spans="2:3" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B32" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C32" s="2">
         <v>15</v>
@@ -914,7 +914,7 @@
     </row>
     <row r="33" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -922,7 +922,7 @@
     </row>
     <row r="34" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B34" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -930,7 +930,7 @@
     </row>
     <row r="35" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B35" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -938,7 +938,7 @@
     </row>
     <row r="36" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -946,7 +946,7 @@
     </row>
     <row r="37" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B37" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -954,7 +954,7 @@
     </row>
     <row r="38" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B38" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -962,37 +962,37 @@
     </row>
     <row r="39" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B39" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>5</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="41" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B41" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B42" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C42" s="2">
         <v>22</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="43" spans="2:5" ht="15.5" x14ac:dyDescent="0.35">
       <c r="B43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
